--- a/ig/DM-37/ValueSet-JDV-J35-SpecialisationDePriseEnCharge-ROR.xlsx
+++ b/ig/DM-37/ValueSet-JDV-J35-SpecialisationDePriseEnCharge-ROR.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="161">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="163">
   <si>
     <t>Property</t>
   </si>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-26T12:00:00+01:00</t>
+    <t>2024-04-26T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -487,6 +487,12 @@
   </si>
   <si>
     <t>Troubles du neurodéveloppement à prédominance motrice (dont trouble développemental de la coordination, mouvements stéréotypés, tics)</t>
+  </si>
+  <si>
+    <t>67</t>
+  </si>
+  <si>
+    <t>Trouble psychotraumatique (dont Troubles Stress Post-Traumatique)</t>
   </si>
   <si>
     <t/>
@@ -765,7 +771,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B67"/>
+  <dimension ref="A1:B68"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -1297,15 +1303,23 @@
         <v>158</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B67" t="s" s="2">
         <v>160</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="B68" t="s" s="2">
+        <v>162</v>
       </c>
     </row>
   </sheetData>
